--- a/quizzes/013_education_reform_assessment_quiz--quizzes.xlsx
+++ b/quizzes/013_education_reform_assessment_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is the size of the school district you work in?</t>
+          <t>Page 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Have you ever used a drag-and-drop interface?</t>
+          <t>Page 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How do you prefer to provide feedback?</t>
+          <t>Page 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1479,46 +1479,46 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>less_than_2,000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Less than 2,000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>page_5_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2,000-5,000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2,000-5,000</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>less_than_2,000</t>
+          <t>5,000-10,000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Less than 2,000</t>
+          <t>5,000-10,000</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2,000-5,000</t>
+          <t>10,000-20,000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2,000-5,000</t>
+          <t>10,000-20,000</t>
         </is>
       </c>
     </row>
@@ -1564,46 +1564,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5,000-10,000</t>
+          <t>more_than_20,000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5,000-10,000</t>
+          <t>More than 20,000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10,000-20,000</t>
+          <t>some_experience</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10,000-20,000</t>
+          <t>Some experience</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>page_6_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>more_than_20,000</t>
+          <t>moderate_experience</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>More than 20,000</t>
+          <t>Moderate experience</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>some_experience</t>
+          <t>significant_experience</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Some experience</t>
+          <t>Significant experience</t>
         </is>
       </c>
     </row>
@@ -1632,46 +1632,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>moderate_experience</t>
+          <t>expert_level</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Moderate experience</t>
+          <t>Expert level</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>significant_experience</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Significant experience</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>page_7_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>expert_level</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Expert level</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1717,46 +1717,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>formal_email</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Formal email</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>formal_letter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>Formal letter</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>formal_email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Formal email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>formal_letter</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Formal letter</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1802,46 +1802,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>formal_email</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phone call</t>
+          <t>Formal email</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>page_9_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>formal_letter</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>Formal letter</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>formal_email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Formal email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>formal_letter</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Formal letter</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1887,53 +1887,53 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phone call</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1950,7 +1950,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>page_11_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_13_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>page_13_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2001,34 +2001,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>some_experience</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Some experience</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>moderate_experience</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Moderate experience</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>some_experience</t>
+          <t>significant_experience</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Some experience</t>
+          <t>Significant experience</t>
         </is>
       </c>
     </row>
@@ -2057,46 +2057,46 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>moderate_experience</t>
+          <t>expert_level</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Moderate experience</t>
+          <t>Expert level</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_15_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>significant_experience</t>
+          <t>formal_email</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Significant experience</t>
+          <t>Formal email</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_15_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>expert_level</t>
+          <t>formal_letter</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Expert level</t>
+          <t>Formal letter</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>formal_email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Formal email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>formal_letter</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Formal letter</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -2142,46 +2142,46 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>page_16_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phone call</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>page_16_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -2210,46 +2210,46 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phone call</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>page_16_choices</t>
+          <t>page_17_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>formal_email</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>Formal email</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>page_16_choices</t>
+          <t>page_17_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>formal_letter</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>Formal letter</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>formal_email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Formal email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>formal_letter</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Formal letter</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -2295,53 +2295,53 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>page_18_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phone call</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>page_18_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>page_18_choices</t>
+          <t>page_19_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>page_18_choices</t>
+          <t>page_19_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2375,7 +2375,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>page_19_choices</t>
+          <t>page_20_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2392,7 +2392,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>page_19_choices</t>
+          <t>page_20_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2409,34 +2409,34 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_21_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_21_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>less_than_5</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Less than 5</t>
+          <t>11-20</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>21-50</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>21-50</t>
         </is>
       </c>
     </row>
@@ -2482,46 +2482,46 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11-20</t>
+          <t>more_than_50</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>11-20</t>
+          <t>More than 50</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_22_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21-50</t>
+          <t>less_than_2,000</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>21-50</t>
+          <t>Less than 2,000</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_22_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>more_than_50</t>
+          <t>2,000-5,000</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>More than 50</t>
+          <t>2,000-5,000</t>
         </is>
       </c>
     </row>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>less_than_2,000</t>
+          <t>5,000-10,000</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Less than 2,000</t>
+          <t>5,000-10,000</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2,000-5,000</t>
+          <t>10,000-20,000</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2,000-5,000</t>
+          <t>10,000-20,000</t>
         </is>
       </c>
     </row>
@@ -2567,80 +2567,80 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5,000-10,000</t>
+          <t>more_than_20,000</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>5,000-10,000</t>
+          <t>More than 20,000</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_23_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>10,000-20,000</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>10,000-20,000</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_23_choices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>more_than_20,000</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>More than 20,000</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>page_23_choices</t>
+          <t>page_24_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>formal_email</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Formal email</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>page_23_choices</t>
+          <t>page_24_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>formal_letter</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Formal letter</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>formal_email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Formal email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>formal_letter</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Formal letter</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -2686,46 +2686,46 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Text message</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>page_24_choices</t>
+          <t>page_25_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>phone_call</t>
+          <t>formal_email</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phone call</t>
+          <t>Formal email</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>page_24_choices</t>
+          <t>page_25_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>in-person_meeting</t>
+          <t>formal_letter</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>In-person meeting</t>
+          <t>Formal letter</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>formal_email</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Formal email</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>formal_letter</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Formal letter</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -2771,44 +2771,10 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>text_message</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
-        <is>
-          <t>Text message</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>phone_call</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Phone call</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>page_25_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>in-person_meeting</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
         <is>
           <t>In-person meeting</t>
         </is>
